--- a/Sample_run/1/student/Control/TC1/GradeDetail.xlsx
+++ b/Sample_run/1/student/Control/TC1/GradeDetail.xlsx
@@ -158,9 +158,6 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN_SENT</x:t>
-  </x:si>
-  <x:si>
     <x:t>PASS</x:t>
   </x:si>
   <x:si>
@@ -170,25 +167,22 @@
     <x:t>Server responding (SYN-ACK)</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SYN_RECEIVED</x:t>
-  </x:si>
-  <x:si>
     <x:t>(Not validated by this test case)</x:t>
   </x:si>
   <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
-    <x:t>ESTABLISHED</x:t>
+    <x:t>Connection established</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>PSH-ACK</x:t>
+    <x:t>PSH, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
     <x:t>S001</x:t>
@@ -197,10 +191,13 @@
     <x:t>{"StudentId":"S001","Name":"John Smith","Major":"Computer Science","Year":3,"GPA":3.5,"Status":"success","Message":"Student information retrieved successfully"}</x:t>
   </x:si>
   <x:si>
-    <x:t>FIN-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN_WAIT</x:t>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server closing connection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client closing connection</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -918,7 +915,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R11"/>
+  <x:dimension ref="A1:R12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -932,7 +929,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="152.853482" style="0" customWidth="1"/>
@@ -1032,7 +1029,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
         <x:v>44</x:v>
@@ -1044,13 +1041,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35818</x:v>
+        <x:v>39806</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -1070,10 +1067,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1085,10 +1082,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
         <x:v>45</x:v>
@@ -1103,10 +1100,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35818</x:v>
+        <x:v>39806</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1114,7 +1111,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>17</x:v>
@@ -1141,10 +1138,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
         <x:v>44</x:v>
@@ -1156,13 +1153,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35818</x:v>
+        <x:v>39806</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1170,7 +1167,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>17</x:v>
@@ -1197,7 +1194,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>54</x:v>
@@ -1209,16 +1206,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35818</x:v>
+        <x:v>39806</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1226,7 +1223,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>17</x:v>
@@ -1253,10 +1250,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>45</x:v>
@@ -1271,10 +1268,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35818</x:v>
+        <x:v>39806</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1282,7 +1279,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>17</x:v>
@@ -1309,7 +1306,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>54</x:v>
@@ -1321,16 +1318,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P7" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>35818</x:v>
+        <x:v>39806</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1338,7 +1335,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>17</x:v>
@@ -1365,10 +1362,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
         <x:v>44</x:v>
@@ -1380,13 +1377,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>35818</x:v>
+        <x:v>39806</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1394,7 +1391,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1421,10 +1418,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>45</x:v>
@@ -1439,10 +1436,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>35818</x:v>
+        <x:v>39806</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1450,7 +1447,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>17</x:v>
@@ -1477,10 +1474,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
         <x:v>44</x:v>
@@ -1492,13 +1489,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>35818</x:v>
+        <x:v>39806</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1506,55 +1503,111 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="0">
+        <x:v>39806</x:v>
+      </x:c>
+      <x:c r="Q11" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
+    </x:row>
+    <x:row r="12" spans="1:18">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="N11" s="0" t="s">
+      <x:c r="N12" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="0">
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>35818</x:v>
-      </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>55</x:v>
+      <x:c r="Q12" s="0">
+        <x:v>39806</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Sample_run/1/student/Control/TC1/GradeDetail.xlsx
+++ b/Sample_run/1/student/Control/TC1/GradeDetail.xlsx
@@ -915,7 +915,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R12"/>
+  <x:dimension ref="A1:R11"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -1041,7 +1041,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>39806</x:v>
+        <x:v>42862</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1100,7 +1100,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>39806</x:v>
+        <x:v>42862</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1153,7 +1153,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>39806</x:v>
+        <x:v>42862</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>39806</x:v>
+        <x:v>42862</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1268,7 +1268,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>39806</x:v>
+        <x:v>42862</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
@@ -1324,7 +1324,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>39806</x:v>
+        <x:v>42862</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>52</x:v>
@@ -1377,7 +1377,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>39806</x:v>
+        <x:v>42862</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1436,7 +1436,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>39806</x:v>
+        <x:v>42862</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>52</x:v>
@@ -1474,10 +1474,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
         <x:v>44</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>39806</x:v>
+        <x:v>42862</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1530,83 +1530,27 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>39806</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>4000</x:v>
+        <x:v>42862</x:v>
       </x:c>
       <x:c r="R11" s="3" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:18">
-      <x:c r="A12" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K12" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="L12" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M12" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N12" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O12" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P12" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q12" s="0">
-        <x:v>39806</x:v>
-      </x:c>
-      <x:c r="R12" s="3" t="s">
         <x:v>52</x:v>
       </x:c>
     </x:row>
